--- a/src/test/resources/testdata/reg_empty.xlsx
+++ b/src/test/resources/testdata/reg_empty.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dr6/Code/stan/core/src/test/resources/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26998B4E-08AE-7742-AD65-5FB764624796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63878D3-B6F9-124C-A06A-C73EF3BB3D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="760" windowWidth="27640" windowHeight="15900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1160" yWindow="760" windowWidth="27640" windowHeight="15900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="60">
   <si>
     <r>
       <t xml:space="preserve">SGP number
@@ -426,6 +426,18 @@
   </si>
   <si>
     <t>Cell class</t>
+  </si>
+  <si>
+    <t>Slot address</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>External barcode</t>
+  </si>
+  <si>
+    <t>XBC1</t>
   </si>
 </sst>
 </file>
@@ -971,10 +983,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:R3"/>
+  <dimension ref="A2:T3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1015,22 +1027,28 @@
         <v>38</v>
       </c>
       <c r="N2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O2" t="s">
         <v>39</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q2" t="s">
         <v>40</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>42</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -1070,16 +1088,22 @@
       <c r="M3">
         <v>1</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="s">
+        <v>57</v>
+      </c>
+      <c r="O3">
         <v>19</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q3" t="s">
         <v>48</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>21</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="S3" t="s">
         <v>49</v>
       </c>
     </row>
